--- a/input/服务器初始化_IP列表.xlsx
+++ b/input/服务器初始化_IP列表.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="8">
   <si>
     <t>host</t>
   </si>
@@ -41,13 +41,16 @@
     <t>password</t>
   </si>
   <si>
-    <t>10.10.10.23</t>
+    <t>192.168.17.132</t>
   </si>
   <si>
     <t>root</t>
   </si>
   <si>
-    <t>Genew@123</t>
+    <t>123@.com</t>
+  </si>
+  <si>
+    <t>192.168.17.128</t>
   </si>
 </sst>
 </file>
@@ -700,8 +703,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="6" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="6">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1049,8 +1052,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="3" outlineLevelCol="3"/>
+  <dimension ref="A1:D3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="2" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="4" width="22.2727272727273" customWidth="1"/>
   </cols>
@@ -1084,20 +1087,23 @@
       </c>
     </row>
     <row r="3" spans="1:4">
-      <c r="A3" s="2"/>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="4"/>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" s="2"/>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="4"/>
+      <c r="A3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="3">
+        <v>22</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>6</v>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="D2" r:id="rId1" display="Genew@123" tooltip="mailto:Genew@123"/>
+    <hyperlink ref="D2" r:id="rId1" display="123@.com"/>
+    <hyperlink ref="D3" r:id="rId1" display="123@.com"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
